--- a/current-software-2026-10-27/Evaluation_Materials/Windows_Manual_Acceptance_Reviewed.xlsx
+++ b/current-software-2026-10-27/Evaluation_Materials/Windows_Manual_Acceptance_Reviewed.xlsx
@@ -922,7 +922,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Real operation progresses228/400; cancellation is acknowledged and displayed record79 is retained.</t>
+          <t>Independent observations: classification progress228/400 withSession record79; separate cancellation acknowledgement withretained classification record78 andSegmentation selected. No continuous before/after sequence established.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Record database/history outcome and close-while-busy cleanup; transient Cancelling screenshot is not required.</t>
+          <t>Record one continuous cancellation and history outcome; separately record close-while-busy cleanup. No transient Cancelling screenshot is required.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
